--- a/web/src/server/assets/quote-report/bang-bao-gia.xlsx
+++ b/web/src/server/assets/quote-report/bang-bao-gia.xlsx
@@ -1,15 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Xpander Eco" state="visible" r:id="rId4"/>
+    <sheet name="Xpander Eco" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -23,9 +39,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 2026</t>
         </r>
@@ -35,9 +51,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 598000000.0</t>
         </r>
@@ -47,9 +63,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: Nâu</t>
         </r>
@@ -59,9 +75,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 95000000.0</t>
         </r>
@@ -71,9 +87,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 59800000.0</t>
         </r>
@@ -83,9 +99,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: Bao tay lái</t>
         </r>
@@ -95,9 +111,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Giá trị mẫu: Phim cách nhiệt </t>
         </r>
@@ -107,9 +123,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 140000.0</t>
         </r>
@@ -119,9 +135,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 02 gối đầu</t>
         </r>
@@ -131,9 +147,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: Thảm lót sàn</t>
         </r>
@@ -143,9 +159,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 140000.0</t>
         </r>
@@ -155,9 +171,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: Ví da đựng hồ sơ</t>
         </r>
@@ -167,9 +183,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Giá trị mẫu: Cam hành trình </t>
         </r>
@@ -179,9 +195,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 1203000.0</t>
         </r>
@@ -191,9 +207,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Giá trị mẫu: Taplo Nhung </t>
         </r>
@@ -203,9 +219,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 2160000.0</t>
         </r>
@@ -215,9 +231,9 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: Tapplo mhung Xpander</t>
         </r>
@@ -227,69 +243,69 @@
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 5000000.0</t>
         </r>
       </text>
     </comment>
-    <comment ref="B26" authorId="0">
+    <comment ref="B24" authorId="0">
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 20000000.0</t>
         </r>
       </text>
     </comment>
-    <comment ref="F27" authorId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 495000000.0</t>
         </r>
       </text>
     </comment>
-    <comment ref="E34" authorId="0">
+    <comment ref="E30" authorId="0">
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 5 Năm</t>
         </r>
       </text>
     </comment>
-    <comment ref="F34" authorId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 60.0</t>
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0">
+    <comment ref="E31" authorId="0">
       <text>
         <r>
           <rPr>
-            <family val="2"/>
             <sz val="10"/>
             <rFont val="Arial"/>
+            <charset val="134"/>
           </rPr>
           <t>Giá trị mẫu: 0.165</t>
         </r>
@@ -300,7 +316,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="74">
   <si>
     <t>BẢNG BÁO GIÁ CHI TIẾT</t>
   </si>
@@ -422,8 +438,7 @@
     <t>Bảo hiểm thân vỏ ( 1.3%)</t>
   </si>
   <si>
-    <t xml:space="preserve">BẢO HIỂM THÂN VỎ XE
-</t>
+    <t>BẢO HIỂM THÂN VỎ XE</t>
   </si>
   <si>
     <t xml:space="preserve">TẶNG </t>
@@ -513,7 +528,7 @@
     <t>Thanh toán tháng</t>
   </si>
   <si>
-    <t xml:space="preserve">Quý khách đặt cọc và ký hợp đồng chúng tôi sẽ tiến hành thẩm
+    <t>Quý khách đặt cọc và ký hợp đồng chúng tôi sẽ tiến hành thẩm
  định và làm hồ sơ ngân hàng, trường hợp ngân hàng không đồng ý cho vay, chúng tôi sẽ hoàn lại 100% tiền cọc</t>
   </si>
   <si>
@@ -529,96 +544,252 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;-* #,##0_-;_-* -_-;_-@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
-    <font>
+  <fonts count="33">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="14"/>
-      <name val="Times New Roman"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color rgb="FF002060"/>
+      <name val="Times New Roman"/>
       <charset val="1"/>
-      <color rgb="FFFF0000"/>
+    </font>
+    <font>
       <sz val="14"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <charset val="1"/>
-      <color rgb="FF002060"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <charset val="1"/>
-      <color theme="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <i/>
-      <charset val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <b/>
-      <charset val="1"/>
-      <color theme="1"/>
-      <sz val="13"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
       <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -631,8 +802,200 @@
         <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -655,189 +1018,681 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F1F1F"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F1F1F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F1F1F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F1F1F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>657360</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1000125</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1828440</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>285480</xdr:rowOff>
+      <xdr:colOff>2171205</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>228330</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="1000125" y="7080250"/>
+          <a:ext cx="1170940" cy="589915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -849,39 +1704,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2019240</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:colOff>2437765</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>850680</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
+      <xdr:colOff>1269205</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>237765</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="2437765" y="7089775"/>
+          <a:ext cx="2031365" cy="589915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -893,39 +1742,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>704880</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>133200</xdr:rowOff>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>104140</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>831600</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>266040</xdr:rowOff>
+      <xdr:colOff>1060170</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>475105</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="933450" y="7901940"/>
+          <a:ext cx="3326765" cy="608965"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -937,39 +1780,33 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>114480</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142920</xdr:rowOff>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1380960</xdr:colOff>
+      <xdr:colOff>1371255</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:rowOff>336070</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="104775" y="209550"/>
+          <a:ext cx="1266190" cy="558165"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -981,60 +1818,73 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="#REF"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Times New Roman" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Times New Roman" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Times New Roman" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Times New Roman" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Times New Roman" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Times New Roman"/>
+        <a:ea typeface="Times New Roman"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1061,7 +1911,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1085,7 +1935,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1145,29 +1995,31 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.21875"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr defaultColWidth="11.2190476190476" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="41.7142857142857" customWidth="1"/>
     <col min="3" max="3" width="3" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="5" max="5" width="30.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="30.2857142857143" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="2" customHeight="1" spans="1:10">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1176,7 +2028,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" ht="2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="2" customHeight="1" spans="1:10">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1185,7 +2037,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" customHeight="1" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +2048,7 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1205,7 +2057,7 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="36" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1214,7 +2066,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="21.75" customHeight="1" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -1225,12 +2077,12 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="21.75" customHeight="1" spans="1:10">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
@@ -1240,514 +2092,475 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7">
-        <f>TODAY()</f>
-        <v>46260</v>
-      </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="E8" s="9"/>
+      <c r="F8" s="10">
+        <f ca="1">TODAY()</f>
+        <v>46267</v>
+      </c>
+      <c r="G8" s="10"/>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="4" t="s">
+      <c r="E9" s="14"/>
+      <c r="F9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="21" customHeight="1" spans="1:10">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="12" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" ht="21" customHeight="1" spans="1:10">
+      <c r="A11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="13" t="e">
+      <c r="B11" s="19" t="e">
         <f>B9-B10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
+      <c r="A12" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="16" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A13" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="18" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18" t="s">
+      <c r="E13" s="28"/>
+      <c r="F13" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="G13" s="28"/>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A14" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18" t="s">
+      <c r="E14" s="28"/>
+      <c r="F14" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="G14" s="28"/>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A15" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="18" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18" t="s">
+      <c r="E15" s="28"/>
+      <c r="F15" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="18"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19"/>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="G15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+    </row>
+    <row r="16" ht="21.75" customHeight="1" spans="1:10">
+      <c r="A16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18" t="s">
+      <c r="E16" s="28"/>
+      <c r="F16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
+      <c r="G16" s="28"/>
+    </row>
+    <row r="17" ht="21" customHeight="1" spans="1:13">
+      <c r="A17" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18" t="s">
+      <c r="E17" s="28"/>
+      <c r="F17" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" hidden="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" ht="24" hidden="1" customHeight="1" spans="1:13">
+      <c r="A18" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="18" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18" t="s">
+      <c r="E18" s="28"/>
+      <c r="F18" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="G18" s="28"/>
+    </row>
+    <row r="19" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A19" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="16" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="20" ht="21" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+    </row>
+    <row r="20" ht="21" customHeight="1" spans="1:13">
+      <c r="A20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="14" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="M20" s="9" t="s">
+      <c r="E20" s="21"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="M20" s="34" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="21" ht="21" customHeight="1" spans="1:13">
+      <c r="A21" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="12">
         <f>SUM(B13:B20)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-    </row>
-    <row r="22" ht="2" customHeight="1" hidden="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-    </row>
-    <row r="23" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
+      <c r="E21" s="28"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+    </row>
+    <row r="22" ht="21" customHeight="1" spans="1:13">
+      <c r="A22" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="26" t="e">
+      <c r="B22" s="37" t="e">
         <f>B11+B21</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="12" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="12"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-    </row>
-    <row r="24" ht="2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+    </row>
+    <row r="23" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A23" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="15" t="s">
+      <c r="B23" s="23"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+    </row>
+    <row r="24" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A24" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B24" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="14" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="29" t="e">
-        <f>B23</f>
+      <c r="E24" s="21"/>
+      <c r="F24" s="40" t="e">
+        <f>B22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G26" s="29"/>
-    </row>
-    <row r="27" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="G24" s="40"/>
+    </row>
+    <row r="25" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A25" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="14" t="s">
+      <c r="B25" s="42"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="32" t="s">
+      <c r="E25" s="21"/>
+      <c r="F25" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="G27" s="32"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="34" t="s">
+      <c r="G25" s="43"/>
+    </row>
+    <row r="26" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A26" s="41"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="32" t="e">
+      <c r="E26" s="46"/>
+      <c r="F26" s="43" t="e">
         <f>B10*10%</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G28" s="32"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+      <c r="G26" s="43"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:13">
+      <c r="A27" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="36" t="e">
-        <f>B23-B26+B27</f>
+      <c r="B27" s="48" t="e">
+        <f>B22-B24+B25</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C29" s="6"/>
-      <c r="D29" s="34" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="34"/>
-      <c r="F29" s="32" t="e">
+      <c r="E27" s="46"/>
+      <c r="F27" s="43" t="e">
         <f>B9*1.3%</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="32"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="36"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="12" t="s">
+      <c r="G27" s="43"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:13">
+      <c r="A28" s="47"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="37" t="e">
-        <f>F26-F27+F28+F29</f>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51" t="e">
+        <f>F24-F25+F26+F27</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G30" s="37"/>
-    </row>
-    <row r="31" ht="2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" ht="2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="G28" s="51"/>
+    </row>
+    <row r="29" ht="18.75" spans="1:13">
+      <c r="A29" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="15" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="17" t="s">
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" ht="18.75" spans="1:13">
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="38" t="s">
+      <c r="E30" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="F34" s="38" t="s">
+      <c r="F30" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="13" t="e">
-        <f>F27/F34</f>
+      <c r="G30" s="55" t="e">
+        <f>F25/F30</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="38"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="17" t="s">
+    <row r="31" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A31" s="52"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="E35" s="39" t="s">
+      <c r="E31" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="39" t="e">
-        <f>E35/12</f>
+      <c r="F31" s="56" t="e">
+        <f>E31/12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G35" s="13" t="e">
-        <f>F35*F27</f>
+      <c r="G31" s="55" t="e">
+        <f>F31*F25</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" ht="22.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="10" t="s">
+    <row r="32" ht="28" customHeight="1" spans="1:13">
+      <c r="A32" s="52"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="40" t="e">
-        <f>G34+G35</f>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="58" t="e">
+        <f>G30+G31</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="38"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="41" t="s">
+    <row r="33" ht="18.75" spans="1:7">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-    </row>
-    <row r="38" ht="29.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-    </row>
-    <row r="39" ht="18.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+    </row>
+    <row r="34" ht="40" customHeight="1" spans="1:7">
+      <c r="A34" s="61"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+    </row>
+    <row r="35" ht="18.75" customHeight="1" spans="1:7">
+      <c r="A35" s="65" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="42" t="s">
+      <c r="B35" s="65"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="65"/>
+      <c r="F35" s="65"/>
+      <c r="G35" s="65"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:7">
+      <c r="A36" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42" t="s">
+      <c r="B36" s="68"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-    </row>
-    <row r="41" ht="78" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-    </row>
-    <row r="42" ht="78" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+    </row>
+    <row r="37" ht="42" customHeight="1" spans="1:7">
+      <c r="A37" s="15"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+    </row>
+    <row r="38" ht="43" customHeight="1" spans="1:7">
+      <c r="A38" s="15"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="A3:G5"/>
+  <mergeCells count="53">
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:E7"/>
@@ -1776,70 +2589,62 @@
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="A34:B38"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="D36:G36"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A3:G5"/>
+    <mergeCell ref="A30:B34"/>
+    <mergeCell ref="D33:G34"/>
+    <mergeCell ref="A37:B38"/>
     <mergeCell ref="D37:G38"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="D41:G42"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="B14">
-      <formula1>'dữ liệu nguồn'!$e$5:$e$8</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B8">
+      <formula1>'[1]#REF'!$G$4:$G$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="B16">
-      <formula1>'dữ liệu nguồn'!$e$11:$e$14</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E9">
+      <formula1>'[1]#REF'!$J$4:$J$15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="B17">
-      <formula1>'dữ liệu nguồn'!$e$16:$e$18</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G9">
+      <formula1>'[1]#REF'!$L$4:$L$14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="B8">
-      <formula1>'dữ liệu nguồn'!$g$4:$g$22</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B14">
+      <formula1>'[1]#REF'!$E$5:$E$8</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E34">
-      <formula1>'dữ liệu nguồn'!$a$5:$a$12</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B16">
+      <formula1>'[1]#REF'!$E$11:$E$14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="E9">
-      <formula1>'dữ liệu nguồn'!$j$4:$j$15</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B17">
+      <formula1>'[1]#REF'!$E$16:$E$18</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="F34">
-      <formula1>'dữ liệu nguồn'!$b$5:$b$12</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E30">
+      <formula1>'[1]#REF'!$A$5:$A$12</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" sqref="G9">
-      <formula1>'dữ liệu nguồn'!$l$4:$l$14</formula1>
-      <formula2>0</formula2>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F30">
+      <formula1>'[1]#REF'!$B$5:$B$12</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="76" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <drawing r:id="rId3"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" scale="76" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>